--- a/output/2026-09-15_01_Croazia_Virovitico-podravska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-15_01_Croazia_Virovitico-podravska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -620,10 +620,9 @@
           <t>072 44 66 22 / 033 300 140</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Catena retail bricolage/fai-da-te generalista (utensili sono uno degli 8 reparti). Non specializzato in utensileria B2B - valutare idoneita come partner. Email non reperita.</t>
+          <t>Catena retail bricolage/fai-da-te generalista (utensili sono uno degli 8 reparti). Non specializzato in utensileria B2B - valutare idoneita come partner. Email non reperita. [DUPLICATO — vedi anche: 2026-09-14_21_Croazia_Virovitico-podravska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -658,7 +657,6 @@
           <t>033 675 706 / 033 673 706</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Produttore di utensili da taglio per legno (lame per seghe a nastro/circolari, punte) venduti come prodotto a clienti B2B (segherie, falegnamerie). Attiva dal 1992. Email non reperita.</t>

--- a/output/2026-09-15_01_Croazia_Virovitico-podravska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-15_01_Croazia_Virovitico-podravska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
